--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261019.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261019.xlsx
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7117525773195876</v>
+        <v>0.7123711340206185</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.09024742268041244</v>
+        <v>0.09086597938144329</v>
       </c>
     </row>
     <row r="8">
@@ -8142,13 +8142,13 @@
         </is>
       </c>
       <c r="H75" s="32" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I75" s="32" t="n">
         <v>26.7</v>
       </c>
       <c r="J75" s="32" t="n">
-        <v>65.3</v>
+        <v>68.3</v>
       </c>
       <c r="K75" s="20" t="n">
         <v>4</v>
@@ -8344,7 +8344,7 @@
     <row r="80">
       <c r="A80" s="34" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 71.2％　対　予定進捗率 62.2％　乖離 +9.0ポイント</t>
+          <t>加重の実績進捗率 71.2％　対　予定進捗率 62.2％　乖離 +9.1ポイント</t>
         </is>
       </c>
     </row>
@@ -14370,14 +14370,14 @@
         </is>
       </c>
       <c r="L73" s="22" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M73" s="23" t="n">
         <v>4</v>
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>**check_ono_ichiji.py が329件を毎回照合し、NGがあれば止まる。現在NGは0件である。****令和8年10月8日に国保連月報からの突合43件を追加した。**それまで月報からの突合は0件で、「961人から862人へ99人減」「給付件数1,303件から1,365件へ」「前年同期比0.9598」といった月報由来の数値が16本のビルダーに手で書かれたまま、月報が1か月増えても誰も気づかない状態だった。**追加した突合で、帳票の構造の読み違いも1件捕まえた**（居宅介護支援と介護予防支援は「居宅サービス計」の外にあり、合計＝3区分計＋総合事業計＋居宅介護支援＋介護予防支援である）。**9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
+          <t>**10月19日に環境が更新され、e-Gov 法令API への接続が許可された。条文番号の原典確認の検査を新設した（check_ono_jobun.py・22件）。****かねて「条文番号は突合の対象外」としていた穴がふさがり、当方の取り違えを2件見つけて直した**（市町村計画に医療計画との整合性の確保の義務があるとしていたもの、障がい2法の調和を第5項としていたもの）。**check_ono_ichiji.py が329件を毎回照合し、NGがあれば止まる。現在NGは0件である。****令和8年10月8日に国保連月報からの突合43件を追加した。**それまで月報からの突合は0件で、「961人から862人へ99人減」「給付件数1,303件から1,365件へ」「前年同期比0.9598」といった月報由来の数値が16本のビルダーに手で書かれたまま、月報が1か月増えても誰も気づかない状態だった。**追加した突合で、帳票の構造の読み違いも1件捕まえた**（居宅介護支援と介護予防支援は「居宅サービス計」の外にあり、合計＝3区分計＋総合事業計＋居宅介護支援＋介護予防支援である）。**9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
         </is>
       </c>
       <c r="O73" s="19" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261019.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261019.xlsx
@@ -14377,7 +14377,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>**10月19日に環境が更新され、e-Gov 法令API への接続が許可された。条文番号の原典確認の検査を新設した（check_ono_jobun.py・22件）。****かねて「条文番号は突合の対象外」としていた穴がふさがり、当方の取り違えを2件見つけて直した**（市町村計画に医療計画との整合性の確保の義務があるとしていたもの、障がい2法の調和を第5項としていたもの）。**check_ono_ichiji.py が329件を毎回照合し、NGがあれば止まる。現在NGは0件である。****令和8年10月8日に国保連月報からの突合43件を追加した。**それまで月報からの突合は0件で、「961人から862人へ99人減」「給付件数1,303件から1,365件へ」「前年同期比0.9598」といった月報由来の数値が16本のビルダーに手で書かれたまま、月報が1か月増えても誰も気づかない状態だった。**追加した突合で、帳票の構造の読み違いも1件捕まえた**（居宅介護支援と介護予防支援は「居宅サービス計」の外にあり、合計＝3区分計＋総合事業計＋居宅介護支援＋介護予防支援である）。**9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
+          <t>**10月19日に環境が更新され、e-Gov 法令API への接続が許可された。条文番号の原典確認の検査を新設した（check_ono_jobun.py・67件）。****かねて「条文番号は突合の対象外」としていた穴がふさがり、当方の取り違えを3件見つけて直した**（市町村計画に医療計画との整合性の確保の義務があるとしていたもの、障がい2法の調和を第5項としていたもの、老人福祉法第20条の8を改正の対象外としていたもの）。**同日、v2 API（asof）により「指定した日に効力をもつ条文」も取れることが分かった。** v1 は現行条文しか返さないが、**本計画の期間は令和9年4月1日に始まり、その日に社会福祉法等の一部を改正する法律（令和8年法律第51号）の多くの規定が施行される。計画期間に適用される条文は改正後のものである。**点検は現行34件・第10期初日33件の両方を見るよう改めた。**これにより、新旧対照条文（二次資料）に頼っていた改正後の条項が原典で裏づけられ、未反映の改正も見つかった**（介護保険法第115条の45第3項の特定地域居宅サービス等事業、社会福祉法第106条の6の小規模市町村地域支援連携協働体制整備事業、支援会議の相互連携の相手方が2つでなく5つであること）。**check_ono_ichiji.py が335件を毎回照合し、NGがあれば止まる。現在NGは0件である。****令和8年10月8日に国保連月報からの突合43件を追加した。**それまで月報からの突合は0件で、「961人から862人へ99人減」「給付件数1,303件から1,365件へ」「前年同期比0.9598」といった月報由来の数値が16本のビルダーに手で書かれたまま、月報が1か月増えても誰も気づかない状態だった。**追加した突合で、帳票の構造の読み違いも1件捕まえた**（居宅介護支援と介護予防支援は「居宅サービス計」の外にあり、合計＝3区分計＋総合事業計＋居宅介護支援＋介護予防支援である）。**9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
         </is>
       </c>
       <c r="O73" s="19" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261019.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261019.xlsx
@@ -14377,7 +14377,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>**10月19日に環境が更新され、e-Gov 法令API への接続が許可された。条文番号の原典確認の検査を新設した（check_ono_jobun.py・67件）。****かねて「条文番号は突合の対象外」としていた穴がふさがり、当方の取り違えを3件見つけて直した**（市町村計画に医療計画との整合性の確保の義務があるとしていたもの、障がい2法の調和を第5項としていたもの、老人福祉法第20条の8を改正の対象外としていたもの）。**同日、v2 API（asof）により「指定した日に効力をもつ条文」も取れることが分かった。** v1 は現行条文しか返さないが、**本計画の期間は令和9年4月1日に始まり、その日に社会福祉法等の一部を改正する法律（令和8年法律第51号）の多くの規定が施行される。計画期間に適用される条文は改正後のものである。**点検は現行34件・第10期初日33件の両方を見るよう改めた。**これにより、新旧対照条文（二次資料）に頼っていた改正後の条項が原典で裏づけられ、未反映の改正も見つかった**（介護保険法第115条の45第3項の特定地域居宅サービス等事業、社会福祉法第106条の6の小規模市町村地域支援連携協働体制整備事業、支援会議の相互連携の相手方が2つでなく5つであること）。**check_ono_ichiji.py が335件を毎回照合し、NGがあれば止まる。現在NGは0件である。****令和8年10月8日に国保連月報からの突合43件を追加した。**それまで月報からの突合は0件で、「961人から862人へ99人減」「給付件数1,303件から1,365件へ」「前年同期比0.9598」といった月報由来の数値が16本のビルダーに手で書かれたまま、月報が1か月増えても誰も気づかない状態だった。**追加した突合で、帳票の構造の読み違いも1件捕まえた**（居宅介護支援と介護予防支援は「居宅サービス計」の外にあり、合計＝3区分計＋総合事業計＋居宅介護支援＋介護予防支援である）。**9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
+          <t>**10月19日に環境が更新され、e-Gov 法令API への接続が許可された。条文番号の原典確認の検査を新設した（check_ono_jobun.py・89件）。****かねて「条文番号は突合の対象外」としていた穴がふさがり、当方の取り違えを3件見つけて直した**（市町村計画に医療計画との整合性の確保の義務があるとしていたもの、障がい2法の調和を第5項としていたもの、老人福祉法第20条の8を改正の対象外としていたもの）。なお、18歳以上の方の呼び方は法律の語（医療的ケア児等）にそろえた（基本指針の改正案は「医療的ケア者」も定義して用いており、誤りではない）。**同日、v2 API（asof）により「指定した日に効力をもつ条文」も取れることが分かった。** v1 は現行条文しか返さないが、**本計画の期間は令和9年4月1日に始まり、その日に社会福祉法等の一部を改正する法律（令和8年法律第51号）の多くの規定が施行される。計画期間に適用される条文は改正後のものである。**点検は現行34件・第10期初日33件の両方を見るよう改めた。**これにより、新旧対照条文（二次資料）に頼っていた改正後の条項が原典で裏づけられ、未反映の改正も見つかった**（介護保険法第115条の45第3項の特定地域居宅サービス等事業、社会福祉法第106条の6の小規模市町村地域支援連携協働体制整備事業、支援会議の相互連携の相手方が2つでなく5つであること、医療的ケア児支援法の題名そのものが改まること）。**政令・省令も取れることが分かり、保険料の標準乗率13件を介護保険法施行令第38条第1項と突き合わせた**（13件すべて一致）。**あわせて、特定地域・小規模市町村の基準を定める厚生労働省令が令和8年10月19日現在まだ公布されていないことを、施行規則の現物で確かめた。** 「当方の環境から取得できない」と「まだ公布されていない」を分けて書けるようになった。**check_ono_ichiji.py が335件を毎回照合し、NGがあれば止まる。現在NGは0件である。****令和8年10月8日に国保連月報からの突合43件を追加した。**それまで月報からの突合は0件で、「961人から862人へ99人減」「給付件数1,303件から1,365件へ」「前年同期比0.9598」といった月報由来の数値が16本のビルダーに手で書かれたまま、月報が1か月増えても誰も気づかない状態だった。**追加した突合で、帳票の構造の読み違いも1件捕まえた**（居宅介護支援と介護予防支援は「居宅サービス計」の外にあり、合計＝3区分計＋総合事業計＋居宅介護支援＋介護予防支援である）。**9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
         </is>
       </c>
       <c r="O73" s="19" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261019.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261019.xlsx
@@ -1312,7 +1312,7 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>**あわせて、介護給付費準備基金の保有額が12.0百万円しかないことが判明した。**第9期は基金取崩35.0百万円を見込んでいた。歳入歳出差引残額は144.2百万円あるため、繰越金として滞留している。令和4年度末の基金は120.0百万円で、令和5年度末に1桁減っており、確認を要する。</t>
+          <t>**あわせて、年報 様式4の介護給付費準備基金の保有額が、令和4年度末120.0百万円から令和5年度末12.0百万円へ1桁減っていることが分かった。**第9期は基金取崩35.0百万円を見込んでいた。歳入歳出差引残額は144.2百万円ある。**その後、町の財務書類で令和5年度末の残高は120.0百万円と確かめられた（令和8年10月21日）。**年報 様式4の保有額は財務書類と合わない。</t>
         </is>
       </c>
     </row>
@@ -1548,17 +1548,17 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の保有額が12.0百万円しかない</t>
+          <t>介護給付費準備基金の残高（年報 様式4と財務書類の不一致）</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>第9期が見込んだ基金取崩35.0百万円は実行できない。保険料水準の判断に直結する</t>
+          <t>取崩額の判断に直結する。残高は令和5年度末120.0百万円、令和8年度末見込210.0百万円（町の財務書類・予算書）</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>**令和4年度末120.0百万円から令和5年度末12.0百万円へ1桁減っている。取崩実績か入力誤りかを町に確認する。繰越金144.2百万円の基金積立も選択肢**</t>
+          <t>**令和7年度末の残高（財産に関する調書）を町に確認する。取崩しの3案（0／105.0／210.0百万円）を協議会に諮る**</t>
         </is>
       </c>
       <c r="E63" s="13" t="n"/>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>**令和7年度の様式4が全て0で未入力。また基金保有額が令和4年度末120百万円から令和5年度末12百万円へ1桁減っており、取崩実績か入力誤りかの確認が要る**</t>
+          <t>**令和7年度の様式4が全て0で未入力。年報 様式4の基金保有額（令和5・6年度末12百万円）は財務書類と合わない。基金は令和8年度末見込210.0百万円。令和7年度末の残高（財産に関する調書）の確認が要る**</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="M74" s="19" t="inlineStr">
         <is>
-          <t>**一般介護予防事業費と包括的支援事業・任意事業費の事業別内訳、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、第9期が見込んだ基金取崩35,000千円に対し基金保有額が12,000千円しかない点の確認が要る（しかも年報の残高の系列に矛盾がある）**</t>
+          <t>**一般介護予防事業費と包括的支援事業・任意事業費の事業別内訳、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、令和7年度末の基金残高（財産に関する調書）の確認が要る。第9期が見込んだ基金取崩35,000千円は残高の範囲内で実行できる**</t>
         </is>
       </c>
     </row>
@@ -9874,12 +9874,12 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>**年報 様式4により令和6年度まで確定。歳入歳出差引残額144.2百万円、介護給付費準備基金の保有額12.0百万円。**保険料収納率は令和7年度99.35％（様式3）</t>
+          <t>**年報 様式4により令和6年度まで確定。歳入歳出差引残額144.2百万円。介護給付費準備基金の残高は令和5年度末120.0百万円（町の財務書類）。**保険料収納率は令和7年度99.35％（様式3）</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
         <is>
-          <t>**令和7年度の様式4が全て0で未入力。また基金保有額が令和4年度末120百万円から令和5年度末12百万円へ1桁減っており、取崩実績か入力誤りかの確認が要る**</t>
+          <t>**令和7年度の様式4が全て0で未入力。年報 様式4の基金保有額（令和5・6年度末12百万円）は財務書類と合わない。基金は令和8年度末見込210.0百万円。令和7年度末の残高（財産に関する調書）の確認が要る**</t>
         </is>
       </c>
       <c r="P18" s="24" t="n"/>
@@ -11939,12 +11939,12 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>**9月28日に、調整交付金見込額の基数を訂正した。基数は調整交付金相当額（5％）と同じ（標準給付費＋総合事業費）であり、標準給付費のみとしていたのは誤りだった。見える化システムの出力と1円まで照合し、第9期の実数でも検算した（誤差0.3％）。訂正による差は月額47円で、保険料基準額は6,048円（切上げ6,100円）である。****所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.485／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替え、あわせて所得段階別の割合を軽減前の標準割合に訂正した結果、保険料基準額は月額6,048円（基金取崩なし）、5,997円（保有額12,000千円を全額取崩）、5,808円（第9期と同じ35,000千円を取崩）となった。**第9期は6,600円。負担割合が24％になると6,364円。従前の方式（令和5〜7年度の3年平均の伸び）では6,402円であり、比較のケースとして残している。**9月25日に、保険料基準額の算定に用いる所得段階別の割合を軽減後の賦課割合（0.285／0.485／0.685）から軽減前の標準割合（0.455／0.685／0.690）に訂正した。**軽減相当額は別枠の公費（国1/2・県1/4・町1/4）で補填され、保険料収納必要額から控除されないためである。第9期計画の補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.974も軽減前でしか再現できない（軽減後だと0.93台）。見える化システムの「①標準段階区分・割合」の画面でも0.4550／0.6850／0.6900が固定表示されることを同日の画面で確認した。**あわせて調整交付金の見込交付割合を、第9期からの逆算6.148％から算式（（第1号負担割合＋5％）－第1号負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数）による5.533％に改めた。**2つの訂正は互いに打ち消し合い、保険料基準額は月額115円下がった※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
+          <t>**9月28日に、調整交付金見込額の基数を訂正した。基数は調整交付金相当額（5％）と同じ（標準給付費＋総合事業費）であり、標準給付費のみとしていたのは誤りだった。見える化システムの出力と1円まで照合し、第9期の実数でも検算した（誤差0.3％）。訂正による差は月額47円で、保険料基準額は6,048円（切上げ6,100円）である。****所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.485／0.685で国の標準より低い）、収納率99.35％、基金残高（町の財務書類。令和8年度末見込210,000千円）を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替え、あわせて所得段階別の割合を軽減前の標準割合に訂正した結果、保険料基準額は月額6,048円（基金取崩なし）となった。****10月21日に基金残高を町の財務書類で確かめ、取崩しの3案（0／105,000／210,000千円）で月額6,053円／5,194円／4,334円とした（地域支援事業費の基準の更新を含む）。**第9期は6,600円。負担割合が24％になると6,364円。従前の方式（令和5〜7年度の3年平均の伸び）では6,402円であり、比較のケースとして残している。**9月25日に、保険料基準額の算定に用いる所得段階別の割合を軽減後の賦課割合（0.285／0.485／0.685）から軽減前の標準割合（0.455／0.685／0.690）に訂正した。**軽減相当額は別枠の公費（国1/2・県1/4・町1/4）で補填され、保険料収納必要額から控除されないためである。第9期計画の補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.974も軽減前でしか再現できない（軽減後だと0.93台）。見える化システムの「①標準段階区分・割合」の画面でも0.4550／0.6850／0.6900が固定表示されることを同日の画面で確認した。**あわせて調整交付金の見込交付割合を、第9期からの逆算6.148％から算式（（第1号負担割合＋5％）－第1号負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数）による5.533％に改めた。**2つの訂正は互いに打ち消し合い、保険料基準額は月額115円下がった※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
         </is>
       </c>
       <c r="O43" s="19" t="inlineStr">
         <is>
-          <t>**一般介護予防事業費と包括的支援事業・任意事業費の事業別内訳、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、第9期が見込んだ基金取崩35,000千円に対し基金保有額が12,000千円しかない点の確認が要る（しかも年報の残高の系列に矛盾がある）**</t>
+          <t>**一般介護予防事業費と包括的支援事業・任意事業費の事業別内訳、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、令和7年度末の基金残高（財産に関する調書）の確認が要る。第9期が見込んだ基金取崩35,000千円は残高の範囲内で実行できる**</t>
         </is>
       </c>
       <c r="P43" s="24" t="n"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>**年報 様式1 所得段階別・様式3・様式4で取得。基金保有額が令和4年度末120百万円→令和5年度末12百万円と1桁減っており要確認**</t>
+          <t>**年報 様式1 所得段階別・様式3・様式4で取得。様式4の基金保有額は財務書類と合わないため、10/21に町の財務書類で令和5年度末120百万円を確認**</t>
         </is>
       </c>
     </row>
@@ -17582,22 +17582,22 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>財政余剰の取扱いと基金残高の不整合</t>
+          <t>財政余剰の取扱いと基金残高</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>**年報 様式4で、歳入歳出差引残額は令和6年度末144.2百万円ある一方、介護給付費準備基金の保有額は12.0百万円しかない。**しかも令和4年度末は120.0百万円で、令和5年度末に1桁減っている。第9期は基金取崩35.0百万円を見込んでいた</t>
+          <t>**年報 様式4で、歳入歳出差引残額は令和6年度末144.2百万円。介護給付費準備基金の残高は町の財務書類で令和5年度末120.0百万円、令和8年度末見込210.0百万円。**年報 様式4の保有額（令和5・6年度末12.0百万円）は財務書類と合わない。第9期は基金取崩35.0百万円を見込んでいた</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>**基金が12百万円しかなければ35百万円の取崩は実行できない。しかも繰入金（取崩し）は令和3〜6年度とも0円で、残高だけが1桁減っており、年報の系列自体に矛盾がある。**見込量の試算で算式を通すと、保険料基準額は取崩なしで月額6,558円、保有額12百万円を全額取り崩して6,456円、第9期と同じ35百万円で6,259円となる（第9期は6,600円）。**基金の扱いだけで月額300円動く**</t>
+          <t>**取崩し（繰入金）は平成30年度以降0円。**保険料基準額は取崩なしで月額6,053円、105.0百万円（見込の半分）で5,194円、210.0百万円（全額）で4,334円となる（第9期は6,600円）。**基金の扱いで月額1,700円余り動く**</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>取崩実績か入力誤りかを町に確認したうえで、余剰の還元（据置・引下げ・繰越金の基金積立）をケースC5・C6として算定する</t>
+          <t>令和7年度末の残高（財産に関する調書）を町に確認したうえで、取崩しの3案を協議会に諮る</t>
         </is>
       </c>
       <c r="F8" s="25" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261019.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261019.xlsx
@@ -1368,7 +1368,7 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>**あわせて、調整交付金見込額の算式を訂正した。**基数は調整交付金相当額（5％）と同じ（標準給付費＋総合事業費）であり、標準給付費のみとしていたのは誤りだった。システムの出力と1円まで照合し、第9期の実数でも検算している（誤差0.3％）。訂正による差は月額47円で、保険料基準額は6,048円（切上げ6,100円）である。</t>
+          <t>**調整交付金見込額の基数は、調整交付金相当額（5％）と同じ（標準給付費＋総合事業費）としている。**システムの出力と1円まで照合し、第9期の実数でも検算している（誤差0.3％）。保険料基準額は6,048円（切上げ6,100円）である。</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>**成果品は、素案が第6版（84表・図3点）、協議会資料が第2版（49表・図9点）に達した。**素案には「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の適正化の記述を実際の得点に合わせて訂正した。**あわせて打合せ資料一式（次第・現在地と論点・決定依頼事項一覧・打合せ記録）を作成した。決めていただくこと11件、いただきたい資料15件である。****ここから先は当方の作業ではなく町の意思決定が律速になる。**</t>
+          <t>**成果品は、素案が第6版（84表・図3点）、協議会資料が第2版（49表・図9点）に達した。**素案には「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の適正化の記述を実際の得点に合わせた。**あわせて打合せ資料一式（次第・現在地と論点・決定依頼事項一覧・打合せ記録）を作成した。決めていただくこと11件、いただきたい資料15件である。****ここから先は当方の作業ではなく町の意思決定が律速になる。**</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="M21" s="19" t="inlineStr">
         <is>
-          <t>―　**9月29日に調査結果報告書の原本（104頁）を受領し、集計値を1件ずつ突き合わせた（286件・NG0）。**認知症の設問の項目名を1件訂正し、報告書そのものの食い違い3件を注記した</t>
+          <t>―　**9月29日に調査結果報告書の原本（104頁）を受領し、集計値を1件ずつ突き合わせた（286件・NG0）。**認知症の設問の項目名を原本に合わせ、報告書そのものの食い違い3件を注記した</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="M69" s="19" t="inlineStr">
         <is>
-          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値の誤りを2件正した。**①所得第2段階の乗率を年報 様式1 所得段階別の令和7年度の値により0.486としたが、**これは誤りで0.485が正しい**（9月25日に再訂正）。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和6年度は485であり、令和7年度の486が入力誤りである。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
+          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値2件を原本で確かめた。**①所得第2段階の乗率は0.485とした。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和7年度は486となっているが、令和6年度は485である。②所得第1〜3段階の割合は、1,094人÷3,443人で31.8％である。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
         </is>
       </c>
     </row>
@@ -10036,7 +10036,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>**9月28日に市町村分の集計表と評価指標を受領し、小野町の得点を項目ごとに整理した（21_給付適正化・交付金／取りまとめ9章・22表・図4点）。****令和8年度交付金は537点／800点で市町村分の平均454.8点を82点上回り、市町村分1,536のうち258位・県内13位／59である。****ただし受領したのは市町村分のみで、公表順位の母数は広域連合を含む1,741保険者。258位は公表順位ではない**（令和7年度は表内1,339位に対し公表1,513位）。**介護給付適正化（推進Ⅱ）は84点で平均を上回る強みであり、体制・取組68点は配点満点。医療情報との突合は全保険者の上位1割。0点はケアプラン点検の実施割合（配点16点）だけである。****主要3事業の「実施」は該当状況調査に対する町の回答（予定を含む）であり、実施の内容は確かめられていない。****また体制・取組68点の根拠となっている文書が確認できていない。第9期計画本文には主要3事業の記載はあるが、評価指標も毎年度の定量的な目標も書かれていない。****8つの目標のうち全国平均を下回るのは支援Ⅲ（在宅医療・在宅介護連携）のみで、55点・県内39位。評価指標が求める4つの場面ごとの目指すべき姿が設定されていないことによる。****素案 第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の適正化の記述を実際の得点に合わせて訂正した。****なお、それまで用いていた見える化システムの値（W126〜W137）は令和6年度交付金（233点）のものであり、2年前の状況だった。**9月25日に令和8年度の評価指標と全国集計（都道府県分）を受領し、協議会資料として整理している（08_協議会資料）。福島県は令和7年度468点・42位から令和8年度530点・26位へ上がり、伸び幅＋62点は47都道府県で3位。ただし全国平均535.6点に届かず、東北6県では5番目。**全国の6割以上が得点していて福島県が0点の項目が21件あり、うち認知症施策に関する市町村支援（全国の93.6％が得点）、チームオレンジ設置状況（70.2％）、介護予防等と保健事業の一体的実施に向けた環境整備ウ・エ・オ（80〜83％）は小野町の施策に直に効く。****県の支援が薄い領域として、素案は町が自前で組み立てる前提で書く。****令和8年度に成果指向型配分枠（100点・800点とは別枠）が新設され、対象層の特定とアウトプット／アウトカム指標の分離、目標値の記載を求めている。第4章の成果指標42件のうち38件が目標値未設定であり、整理の仕方が交付金の配分に直に効く。**評価結果は計画本文には載せず毎年度の協議会資料として扱う（評価結果を外部の議論の場で検証すること自体が指標の要件であるため）。**10月4日に成果指標群（目標Ⅳ）の図を作成した（f49_yokaigo）。****15点（令和6年度交付金）から60点（令和8年度）へ伸びており、同じ期間に全国平均はほぼ動いていない（48.6→47.8点）。****0点のまま残るのは健康寿命延伸の状況だけで、性・年齢調整済み要介護2以上の認定率が全国8.99％・県10.09％に対し小野町14.28％と高いことによる**</t>
+          <t>**9月28日に市町村分の集計表と評価指標を受領し、小野町の得点を項目ごとに整理した（21_給付適正化・交付金／取りまとめ9章・22表・図4点）。****令和8年度交付金は537点／800点で市町村分の平均454.8点を82点上回り、市町村分1,536のうち258位・県内13位／59である。****ただし受領したのは市町村分のみで、公表順位の母数は広域連合を含む1,741保険者。258位は公表順位ではない**（令和7年度は表内1,339位に対し公表1,513位）。**介護給付適正化（推進Ⅱ）は84点で平均を上回る強みであり、体制・取組68点は配点満点。医療情報との突合は全保険者の上位1割。0点はケアプラン点検の実施割合（配点16点）だけである。****主要3事業の「実施」は該当状況調査に対する町の回答（予定を含む）であり、実施の内容は確かめられていない。****また体制・取組68点の根拠となっている文書が確認できていない。第9期計画本文には主要3事業の記載はあるが、評価指標も毎年度の定量的な目標も書かれていない。****8つの目標のうち全国平均を下回るのは支援Ⅲ（在宅医療・在宅介護連携）のみで、55点・県内39位。評価指標が求める4つの場面ごとの目指すべき姿が設定されていないことによる。****素案 第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の適正化の記述を実際の得点に合わせた。****なお、それまで用いていた見える化システムの値（W126〜W137）は令和6年度交付金（233点）のものであり、2年前の状況だった。**9月25日に令和8年度の評価指標と全国集計（都道府県分）を受領し、協議会資料として整理している（08_協議会資料）。福島県は令和7年度468点・42位から令和8年度530点・26位へ上がり、伸び幅＋62点は47都道府県で3位。ただし全国平均535.6点に届かず、東北6県では5番目。**全国の6割以上が得点していて福島県が0点の項目が21件あり、うち認知症施策に関する市町村支援（全国の93.6％が得点）、チームオレンジ設置状況（70.2％）、介護予防等と保健事業の一体的実施に向けた環境整備ウ・エ・オ（80〜83％）は小野町の施策に直に効く。****県の支援が薄い領域として、素案は町が自前で組み立てる前提で書く。****令和8年度に成果指向型配分枠（100点・800点とは別枠）が新設され、対象層の特定とアウトプット／アウトカム指標の分離、目標値の記載を求めている。第4章の成果指標42件のうち38件が目標値未設定であり、整理の仕方が交付金の配分に直に効く。**評価結果は計画本文には載せず毎年度の協議会資料として扱う（評価結果を外部の議論の場で検証すること自体が指標の要件であるため）。**10月4日に成果指標群（目標Ⅳ）の図を作成した（f49_yokaigo）。****15点（令和6年度交付金）から60点（令和8年度）へ伸びており、同じ期間に全国平均はほぼ動いていない（48.6→47.8点）。****0点のまま残るのは健康寿命延伸の状況だけで、性・年齢調整済み要介護2以上の認定率が全国8.99％・県10.09％に対し小野町14.28％と高いことによる**</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="O26" s="19" t="inlineStr">
         <is>
-          <t>―　**9月29日に調査結果報告書の原本（104頁）を受領し、集計値を1件ずつ突き合わせた（286件・NG0）。**認知症の設問の項目名を1件訂正し、報告書そのものの食い違い3件を注記した</t>
+          <t>―　**9月29日に調査結果報告書の原本（104頁）を受領し、集計値を1件ずつ突き合わせた（286件・NG0）。**認知症の設問の項目名を原本に合わせ、報告書そのものの食い違い3件を注記した</t>
         </is>
       </c>
       <c r="P26" s="24" t="n"/>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>**9月28日に、調整交付金見込額の基数を訂正した。基数は調整交付金相当額（5％）と同じ（標準給付費＋総合事業費）であり、標準給付費のみとしていたのは誤りだった。見える化システムの出力と1円まで照合し、第9期の実数でも検算した（誤差0.3％）。訂正による差は月額47円で、保険料基準額は6,048円（切上げ6,100円）である。****所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.485／0.685で国の標準より低い）、収納率99.35％、基金残高（町の財務書類。令和8年度末見込210,000千円）を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替え、あわせて所得段階別の割合を軽減前の標準割合に訂正した結果、保険料基準額は月額6,048円（基金取崩なし）となった。****10月21日に基金残高を町の財務書類で確かめ、取崩しの3案（0／105,000／210,000千円）で月額6,053円／5,194円／4,334円とした（地域支援事業費の基準の更新を含む）。**第9期は6,600円。負担割合が24％になると6,364円。従前の方式（令和5〜7年度の3年平均の伸び）では6,402円であり、比較のケースとして残している。**9月25日に、保険料基準額の算定に用いる所得段階別の割合を軽減後の賦課割合（0.285／0.485／0.685）から軽減前の標準割合（0.455／0.685／0.690）に訂正した。**軽減相当額は別枠の公費（国1/2・県1/4・町1/4）で補填され、保険料収納必要額から控除されないためである。第9期計画の補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.974も軽減前でしか再現できない（軽減後だと0.93台）。見える化システムの「①標準段階区分・割合」の画面でも0.4550／0.6850／0.6900が固定表示されることを同日の画面で確認した。**あわせて調整交付金の見込交付割合を、第9期からの逆算6.148％から算式（（第1号負担割合＋5％）－第1号負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数）による5.533％に改めた。**2つの訂正は互いに打ち消し合い、保険料基準額は月額115円下がった※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
+          <t>**調整交付金見込額の基数は、調整交付金相当額（5％）と同じ（標準給付費＋総合事業費）としている。見える化システムの出力と1円まで照合し、第9期の実数でも検算した（誤差0.3％）。保険料基準額は6,048円（切上げ6,100円）である。****所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.485／0.685で国の標準より低い）、収納率99.35％、基金残高（町の財務書類。令和8年度末見込210,000千円）を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替え、所得段階別の割合を軽減前の標準割合とした結果、保険料基準額は月額6,048円（基金取崩なし）となった。****10月21日に基金残高を町の財務書類で確かめ、取崩しの3案（0／105,000／210,000千円）で月額6,053円／5,194円／4,334円とした（地域支援事業費の基準の更新を含む）。**第9期は6,600円。負担割合が24％になると6,364円。従前の方式（令和5〜7年度の3年平均の伸び）では6,402円であり、比較のケースとして残している。**保険料基準額の算定に用いる所得段階別の割合は、軽減前の標準割合（0.455／0.685／0.690）としている（軽減後の賦課割合は0.285／0.485／0.685）。**軽減相当額は別枠の公費（国1/2・県1/4・町1/4）で補填され、保険料収納必要額から控除されないためである。第9期計画の補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.974も軽減前でしか再現できない（軽減後だと0.93台）。見える化システムの「①標準段階区分・割合」の画面でも0.4550／0.6850／0.6900が固定表示されることを同日の画面で確認した。**あわせて調整交付金の見込交付割合を、第9期からの逆算6.148％から算式（（第1号負担割合＋5％）－第1号負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数）による5.533％に改めた。**この2点を織り込んだ保険料基準額は、上記のとおりである※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
         </is>
       </c>
       <c r="O43" s="19" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>**第11版（6章＋資料編・127表・図5点・見出し53件・78頁）。****10月15日に、法定記載事項チェック（新設）が見つけた4件の欠落を埋めた。**第6章9「老人福祉事業の量の目標」を新設し（老人福祉法第20条の8第2項・義務）、第1章7に県の意見聴取（介護保険法第117条第14項）、第1章6(2)に実績評価の根拠条文（改正後第9項）を加えた。**法定記載事項21件はすべて○である。**未確定は163箇所（町データ待ち89／協議会で設定55／決定後に記載13／見える化出力待ち6）で、**受託者が算定すべきものは引き続き0件である。****第6版（5章＋資料編・84表・図3点）。****第4章④に「人材の供給制約からみた見込量の妥当性」と「見える化システムによる算定との突合」を加えた。****第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、国の評価指標が求める4つの場面（日常の療養支援・入退院支援・急変時の対応・看取り）ごとの目指すべき姿を掲げた。****基本目標3① の介護給付適正化の記述を、令和8年度交付金の実際の得点に合わせて訂正した**（主要3事業は3つとも実施、医療情報との突合は全国上位1割。0点はケアプラン点検の実施割合だけ）。**項目別の得点そのものは計画本文には置かず、評価から読み取れる中身と協議会への報告手順のみを書いている。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,402円から6,048円（切上げ6,100円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
+          <t>**第11版（6章＋資料編・127表・図5点・見出し53件・78頁）。****10月15日に、法定記載事項チェック（新設）が見つけた4件の欠落を埋めた。**第6章9「老人福祉事業の量の目標」を新設し（老人福祉法第20条の8第2項・義務）、第1章7に県の意見聴取（介護保険法第117条第14項）、第1章6(2)に実績評価の根拠条文（改正後第9項）を加えた。**法定記載事項21件はすべて○である。**未確定は163箇所（町データ待ち89／協議会で設定55／決定後に記載13／見える化出力待ち6）で、**受託者が算定すべきものは引き続き0件である。****第6版（5章＋資料編・84表・図3点）。****第4章④に「人材の供給制約からみた見込量の妥当性」と「見える化システムによる算定との突合」を加えた。****第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、国の評価指標が求める4つの場面（日常の療養支援・入退院支援・急変時の対応・看取り）ごとの目指すべき姿を掲げた。****基本目標3① の介護給付適正化の記述を、令和8年度交付金の実際の得点に合わせて書いた**（主要3事業は3つとも実施、医療情報との突合は全国上位1割。0点はケアプラン点検の実施割合だけ）。**項目別の得点そのものは計画本文には置かず、評価から読み取れる中身と協議会への報告手順のみを書いている。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,402円から6,048円（切上げ6,100円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
         </is>
       </c>
       <c r="O47" s="19" t="inlineStr">
         <is>
-          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値の誤りを2件正した。**①所得第2段階の乗率を年報 様式1 所得段階別の令和7年度の値により0.486としたが、**これは誤りで0.485が正しい**（9月25日に再訂正）。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和6年度は485であり、令和7年度の486が入力誤りである。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
+          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値2件を原本で確かめた。**①所得第2段階の乗率は0.485とした。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和7年度は486となっているが、令和6年度は485である。②所得第1〜3段階の割合は、1,094人÷3,443人で31.8％である。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
         </is>
       </c>
       <c r="P47" s="20" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>**10月19日に環境が更新され、e-Gov 法令API への接続が許可された。条文番号の原典確認の検査を新設した（check_ono_jobun.py・89件）。****かねて「条文番号は突合の対象外」としていた穴がふさがり、当方の取り違えを3件見つけて直した**（市町村計画に医療計画との整合性の確保の義務があるとしていたもの、障がい2法の調和を第5項としていたもの、老人福祉法第20条の8を改正の対象外としていたもの）。なお、18歳以上の方の呼び方は法律の語（医療的ケア児等）にそろえた（基本指針の改正案は「医療的ケア者」も定義して用いており、誤りではない）。**同日、v2 API（asof）により「指定した日に効力をもつ条文」も取れることが分かった。** v1 は現行条文しか返さないが、**本計画の期間は令和9年4月1日に始まり、その日に社会福祉法等の一部を改正する法律（令和8年法律第51号）の多くの規定が施行される。計画期間に適用される条文は改正後のものである。**点検は現行34件・第10期初日33件の両方を見るよう改めた。**これにより、新旧対照条文（二次資料）に頼っていた改正後の条項が原典で裏づけられ、未反映の改正も見つかった**（介護保険法第115条の45第3項の特定地域居宅サービス等事業、社会福祉法第106条の6の小規模市町村地域支援連携協働体制整備事業、支援会議の相互連携の相手方が2つでなく5つであること、医療的ケア児支援法の題名そのものが改まること）。**政令・省令も取れることが分かり、保険料の標準乗率13件を介護保険法施行令第38条第1項と突き合わせた**（13件すべて一致）。**あわせて、特定地域・小規模市町村の基準を定める厚生労働省令が令和8年10月19日現在まだ公布されていないことを、施行規則の現物で確かめた。** 「当方の環境から取得できない」と「まだ公布されていない」を分けて書けるようになった。**check_ono_ichiji.py が335件を毎回照合し、NGがあれば止まる。現在NGは0件である。****令和8年10月8日に国保連月報からの突合43件を追加した。**それまで月報からの突合は0件で、「961人から862人へ99人減」「給付件数1,303件から1,365件へ」「前年同期比0.9598」といった月報由来の数値が16本のビルダーに手で書かれたまま、月報が1か月増えても誰も気づかない状態だった。**追加した突合で、帳票の構造の読み違いも1件捕まえた**（居宅介護支援と介護予防支援は「居宅サービス計」の外にあり、合計＝3区分計＋総合事業計＋居宅介護支援＋介護予防支援である）。**9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
+          <t>**10月19日に環境が更新され、e-Gov 法令API への接続が許可された。条文番号の原典確認の検査を新設した（check_ono_jobun.py・89件）。****かねて「条文番号は突合の対象外」としていた穴がふさがり、当方の取り違えを3件見つけて直した**（市町村計画に医療計画との整合性の確保の義務があるとしていたもの、障がい2法の調和を第5項としていたもの、老人福祉法第20条の8を改正の対象外としていたもの）。なお、18歳以上の方の呼び方は法律の語（医療的ケア児等）にそろえた（基本指針の改正案は「医療的ケア者」も定義して用いており、誤りではない）。**同日、v2 API（asof）により「指定した日に効力をもつ条文」も取れることが分かった。** v1 は現行条文しか返さないが、**本計画の期間は令和9年4月1日に始まり、その日に社会福祉法等の一部を改正する法律（令和8年法律第51号）の多くの規定が施行される。計画期間に適用される条文は改正後のものである。**点検は現行34件・第10期初日33件の両方を見るよう改めた。**これにより、新旧対照条文（二次資料）に頼っていた改正後の条項が原典で裏づけられ、未反映の改正も見つかった**（介護保険法第115条の45第3項の特定地域居宅サービス等事業、社会福祉法第106条の6の小規模市町村地域支援連携協働体制整備事業、支援会議の相互連携の相手方が2つでなく5つであること、医療的ケア児支援法の題名そのものが改まること）。**政令・省令も取れることが分かり、保険料の標準乗率13件を介護保険法施行令第38条第1項と突き合わせた**（13件すべて一致）。**あわせて、特定地域・小規模市町村の基準を定める厚生労働省令が令和8年10月19日現在まだ公布されていないことを、施行規則の現物で確かめた。** 「当方の環境から取得できない」と「まだ公布されていない」を分けて書けるようになった。**check_ono_ichiji.py が335件を毎回照合し、NGがあれば止まる。現在NGは0件である。****令和8年10月8日に国保連月報からの突合43件を追加した。**それまで月報からの突合は0件で、「961人から862人へ99人減」「給付件数1,303件から1,365件へ」「前年同期比0.9598」といった月報由来の数値が16本のビルダーに手で書かれたまま、月報が1か月増えても誰も気づかない状態だった。**追加した突合で、帳票の構造の読み違いも1件捕まえた**（居宅介護支援と介護予防支援は「居宅サービス計」の外にあり、合計＝3区分計＋総合事業計＋居宅介護支援＋介護予防支援である）。**9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。問36の54.1％は**「地域での見守りや声掛け」**であり、素案・協議会資料・調査結果の分析・交付金の4点で原本と同じ項目名としている。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
         </is>
       </c>
       <c r="O73" s="19" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="F2" s="19" t="inlineStr">
         <is>
-          <t>**第1号被保険者1人あたり給付月額の県内順位を23位・30位から28位・33位に訂正し、認定率の「県内2位」に年度（令和7年3月末）を付した。見える化の定員の年度も令和7年度から令和6年度に直した**</t>
+          <t>**第1号被保険者1人あたり給付月額の県内順位は28位・33位であることを確かめ、認定率の「県内2位」に年度（令和7年3月末）を付した。見える化の定員は令和6年度の値であることを明記した**</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18061,7 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>**調整交付金見込額の基数を、標準給付費のみから（標準給付費＋総合事業費）に訂正した。**調整交付金相当額（5％）と同じ基数である</t>
+          <t>**調整交付金見込額の基数は、（標準給付費＋総合事業費）とする。**調整交付金相当額（5％）と同じ基数である</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="F4" s="19" t="inlineStr">
         <is>
-          <t>**見える化システムの出力と1円まで照合し、第9期の実数でも検算した（誤差0.3％）。訂正による差は月額47円で、保険料基準額は6,048円（切上げ6,100円）である。町にはまだお出ししていない段階での訂正である**</t>
+          <t>**見える化システムの出力と1円まで照合し、第9期の実数でも検算した（誤差0.3％）。保険料基準額は6,048円（切上げ6,100円）である**</t>
         </is>
       </c>
     </row>
